--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008415679646344133</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9819263</v>
+        <v>4802236</v>
       </c>
       <c r="L2" t="n">
-        <v>6217749</v>
+        <v>2976057</v>
       </c>
       <c r="M2" t="n">
-        <v>1696216</v>
+        <v>780023</v>
       </c>
       <c r="N2" t="n">
-        <v>111608</v>
+        <v>44659</v>
       </c>
       <c r="O2" t="n">
-        <v>967147</v>
+        <v>459073</v>
       </c>
       <c r="P2" t="n">
-        <v>370014</v>
+        <v>179046</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999980926513672</v>
+        <v>0.9999983906745911</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9766207337379456</v>
+        <v>0.9557753801345825</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9407639503479004</v>
+        <v>0.8941516876220703</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9252482652664185</v>
+        <v>0.867652416229248</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8538335561752319</v>
+        <v>0.7122306823730469</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9458021521568298</v>
+        <v>0.8997268080711365</v>
       </c>
       <c r="W2" t="n">
-        <v>0.965836763381958</v>
+        <v>0.9331582188606262</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -795,16 +795,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9819263</v>
+        <v>4802236</v>
       </c>
       <c r="E3" t="n">
-        <v>250740</v>
+        <v>228883</v>
       </c>
       <c r="F3" t="n">
-        <v>2479</v>
+        <v>2466</v>
       </c>
       <c r="G3" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H3" t="n">
         <v>62</v>
@@ -813,109 +813,109 @@
         <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>20033220</v>
+        <v>10016612</v>
       </c>
       <c r="K3" t="n">
-        <v>22351101</v>
+        <v>11073258</v>
       </c>
       <c r="L3" t="n">
-        <v>25753024</v>
+        <v>12717946</v>
       </c>
       <c r="M3" t="n">
-        <v>30658995</v>
+        <v>15278807</v>
       </c>
       <c r="N3" t="n">
-        <v>32462025</v>
+        <v>16222492</v>
       </c>
       <c r="O3" t="n">
-        <v>31586021</v>
+        <v>15769464</v>
       </c>
       <c r="P3" t="n">
-        <v>32259567</v>
+        <v>16123493</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9748067259788513</v>
+        <v>0.9539341330528259</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9544227123260498</v>
+        <v>0.9130821228027344</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9103944301605225</v>
+        <v>0.8371034264564514</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6267682909965515</v>
+        <v>0.5014259219169617</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9502720832824707</v>
+        <v>0.9019594192504883</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9572339653968811</v>
+        <v>0.9263459444046021</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>220570</v>
+        <v>207810</v>
       </c>
       <c r="E4" t="n">
-        <v>6217749</v>
+        <v>2976057</v>
       </c>
       <c r="F4" t="n">
-        <v>74065</v>
+        <v>73207</v>
       </c>
       <c r="G4" t="n">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="H4" t="n">
         <v>1167</v>
@@ -947,109 +947,109 @@
         <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>235063</v>
+        <v>222204</v>
       </c>
       <c r="L4" t="n">
-        <v>391506</v>
+        <v>352301</v>
       </c>
       <c r="M4" t="n">
-        <v>137039</v>
+        <v>118981</v>
       </c>
       <c r="N4" t="n">
-        <v>19106</v>
+        <v>18044</v>
       </c>
       <c r="O4" t="n">
-        <v>55421</v>
+        <v>51163</v>
       </c>
       <c r="P4" t="n">
-        <v>13088</v>
+        <v>12825</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999990463256836</v>
+        <v>0.9999992251396179</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9757128953933716</v>
+        <v>0.954853892326355</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9475440979003906</v>
+        <v>0.9035177230834961</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9177612662315369</v>
+        <v>0.8521041870117188</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7228895425796509</v>
+        <v>0.5885205268859863</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9480318427085876</v>
+        <v>0.9008417129516602</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9615161418914795</v>
+        <v>0.9297395944595337</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8223</v>
+        <v>8140</v>
       </c>
       <c r="E5" t="n">
-        <v>119824</v>
+        <v>105286</v>
       </c>
       <c r="F5" t="n">
-        <v>1696216</v>
+        <v>780023</v>
       </c>
       <c r="G5" t="n">
-        <v>9144</v>
+        <v>8605</v>
       </c>
       <c r="H5" t="n">
-        <v>29188</v>
+        <v>29187</v>
       </c>
       <c r="I5" t="n">
         <v>571</v>
@@ -1080,131 +1080,131 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>253773</v>
+        <v>231902</v>
       </c>
       <c r="L5" t="n">
-        <v>296921</v>
+        <v>283296</v>
       </c>
       <c r="M5" t="n">
-        <v>166950</v>
+        <v>151789</v>
       </c>
       <c r="N5" t="n">
-        <v>66461</v>
+        <v>44405</v>
       </c>
       <c r="O5" t="n">
-        <v>50611</v>
+        <v>49900</v>
       </c>
       <c r="P5" t="n">
-        <v>16531</v>
+        <v>14236</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9999994039535522</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9850322008132935</v>
+        <v>0.9721912145614624</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9789208769798279</v>
+        <v>0.9610769748687744</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9906920790672302</v>
+        <v>0.9834184646606445</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9973800182342529</v>
+        <v>0.9961757063865662</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9967533946037292</v>
+        <v>0.9938110709190369</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9990931153297424</v>
+        <v>0.9983428120613098</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6240</v>
+        <v>6224</v>
       </c>
       <c r="E6" t="n">
-        <v>20037</v>
+        <v>17227</v>
       </c>
       <c r="F6" t="n">
-        <v>30544</v>
+        <v>13359</v>
       </c>
       <c r="G6" t="n">
-        <v>111608</v>
+        <v>44659</v>
       </c>
       <c r="H6" t="n">
-        <v>9193</v>
+        <v>7198</v>
       </c>
       <c r="I6" t="n">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1269,16 +1269,16 @@
         <v>801</v>
       </c>
       <c r="F7" t="n">
-        <v>29623</v>
+        <v>29621</v>
       </c>
       <c r="G7" t="n">
-        <v>8143</v>
+        <v>7650</v>
       </c>
       <c r="H7" t="n">
-        <v>967147</v>
+        <v>459073</v>
       </c>
       <c r="I7" t="n">
-        <v>12022</v>
+        <v>11806</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -1346,13 +1346,13 @@
         <v>328</v>
       </c>
       <c r="G8" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="H8" t="n">
-        <v>15811</v>
+        <v>13549</v>
       </c>
       <c r="I8" t="n">
-        <v>370014</v>
+        <v>179046</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
